--- a/artfynd/A 35003-2021 artfynd.xlsx
+++ b/artfynd/A 35003-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128094578</v>
       </c>
       <c r="B2" t="n">
-        <v>100622</v>
+        <v>100623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2021 artfynd.xlsx
+++ b/artfynd/A 35003-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128094578</v>
       </c>
       <c r="B2" t="n">
-        <v>100623</v>
+        <v>100624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2021 artfynd.xlsx
+++ b/artfynd/A 35003-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128094578</v>
       </c>
       <c r="B2" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2021 artfynd.xlsx
+++ b/artfynd/A 35003-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128094578</v>
       </c>
       <c r="B2" t="n">
-        <v>100625</v>
+        <v>100633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2021 artfynd.xlsx
+++ b/artfynd/A 35003-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128094578</v>
       </c>
       <c r="B2" t="n">
-        <v>100633</v>
+        <v>100726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2021 artfynd.xlsx
+++ b/artfynd/A 35003-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128094578</v>
       </c>
       <c r="B2" t="n">
-        <v>100726</v>
+        <v>100741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2021 artfynd.xlsx
+++ b/artfynd/A 35003-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128094578</v>
       </c>
       <c r="B2" t="n">
-        <v>100741</v>
+        <v>100752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
